--- a/Bases de Dados/Emails.xlsx
+++ b/Bases de Dados/Emails.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaop\Google Drive\Python Impressionador\Projeto_AutomacaoIndicadores\Bases de Dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caieb\OneDrive\Documentos\Meus Projetos - GitGitHub\Automação-de-Processos\Bases de Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3856DD-4A41-42A6-8CEE-9B800498E7C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80F7121-3F50-46A8-A2AB-6AF0089E0CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{EE9D8D8A-F7B1-481B-B9DF-10FF6CFE8B3E}"/>
+    <workbookView xWindow="4188" yWindow="4188" windowWidth="30960" windowHeight="12120" xr2:uid="{EE9D8D8A-F7B1-481B-B9DF-10FF6CFE8B3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -180,63 +183,6 @@
     <t>Diretoria</t>
   </si>
   <si>
-    <t>pythonimpressionador+helena@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+alice@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+laura@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+manuela@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+valentina@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+sophia@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+isabella@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+luiza@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+lorena@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+miguel@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+arthur@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+heitor@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+bernardo@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+davi@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+lorenzo@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+gabriel@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+pedro@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+benjamin@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+diretoria@gmail.com</t>
-  </si>
-  <si>
     <t>Heloisa</t>
   </si>
   <si>
@@ -255,25 +201,82 @@
     <t>Theo</t>
   </si>
   <si>
-    <t>pythonimpressionador+heloisa@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+julia@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+livia@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+cecilia@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+eloa@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+theo@gmail.com</t>
-  </si>
-  <si>
-    <t>pythonimpressionador+maria_luiza@gmail.com</t>
+    <t>caioriberio+helena@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+alice@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+laura@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+manuela@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+valentina@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+sophia@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+isabella@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+heloisa@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+luiza@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+julia@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+lorena@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+livia@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+maria_luiza@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+cecilia@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+eloa@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+miguel@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+arthur@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+heitor@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+bernardo@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+davi@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+theo@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+lorenzo@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+gabriel@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+pedro@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+benjamin@gmail.com</t>
+  </si>
+  <si>
+    <t>caioriberio+diretoria@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -340,9 +343,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -380,7 +383,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -486,7 +489,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +631,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -637,13 +640,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D81E77-7AEF-4DB7-8688-DEDDD091CFFB}">
   <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.62890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.3671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -662,11 +665,11 @@
         <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -674,11 +677,11 @@
         <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -686,10 +689,10 @@
         <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -697,10 +700,10 @@
         <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -708,10 +711,10 @@
         <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -719,10 +722,10 @@
         <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -730,21 +733,21 @@
         <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -752,21 +755,21 @@
         <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -774,21 +777,21 @@
         <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -796,32 +799,32 @@
         <v>46</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -829,10 +832,10 @@
         <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -840,10 +843,10 @@
         <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -851,10 +854,10 @@
         <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -862,10 +865,10 @@
         <v>35</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -873,21 +876,21 @@
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -895,10 +898,10 @@
         <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -906,10 +909,10 @@
         <v>41</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -917,10 +920,10 @@
         <v>43</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -928,10 +931,10 @@
         <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -939,7 +942,7 @@
         <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
